--- a/public/exemplo-carteira-facilitavet.xlsx
+++ b/public/exemplo-carteira-facilitavet.xlsx
@@ -5,93 +5,132 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Leia-me" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="CAT 1" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="CAT 2" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="CAT 3" state="visible" r:id="rId7"/>
+    <sheet sheetId="2" name="FIXOS" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="VARI 1" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="VARI 2" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="26">
-  <si>
-    <t>Uma linha por veterinário. A categoria vem do nome da aba (CAT 1, CAT 2, CAT 3) — não precisa de coluna "Categoria". Marque "2 visitas" quando a clínica funciona por plantão e nem todo mundo está presente no mesmo dia, então uma única visita não alcança todos. Se ainda não souber o nome do veterinário de uma clínica nova, deixe a célula em branco: a clínica entra na carteira mesmo assim.</t>
-  </si>
-  <si>
-    <t>Clínica</t>
-  </si>
-  <si>
-    <t>Nome do veterinário</t>
-  </si>
-  <si>
-    <t>Bairro</t>
-  </si>
-  <si>
-    <t>2 visitas</t>
-  </si>
-  <si>
-    <t>Clínica Pata Feliz</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+  <si>
+    <t>Uma linha por veterinário. A categoria vem do nome da aba: FIXOS, VARI 1 e VARI 2. FREQUENCIA DE VISITA em texto livre: "1x no mês", "2x no mês em dias alternados" (plantão), "1x no mês sempre sexta", "terça ou quinta", "de preferencia quarta", "evitar as sextas". Frequência vazia = fora do mês. Na coluna VISITEI, "colocar dia 16 de outubro" marca a data da visita. No endereço, "NÃO COLOCAR NO ROTEIRO" deixa a clínica fora do roteiro.</t>
+  </si>
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>BAIRRO</t>
+  </si>
+  <si>
+    <t>VISITEI</t>
+  </si>
+  <si>
+    <t>DE ONDE</t>
+  </si>
+  <si>
+    <t>ENDEREÇO</t>
+  </si>
+  <si>
+    <t>FREQUENCIA DE VISITA</t>
   </si>
   <si>
     <t>Dra. Ana Souza</t>
   </si>
   <si>
-    <t>Centro</t>
+    <t>CENTRO</t>
+  </si>
+  <si>
+    <t>SET OK</t>
+  </si>
+  <si>
+    <t>CLÍNICA PATA FELIZ</t>
+  </si>
+  <si>
+    <t>Rua das Flores, 120 - Centro, Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>1x no mês</t>
+  </si>
+  <si>
+    <t>Dr. Bruno Lima</t>
+  </si>
+  <si>
+    <t>Dra. Carla Nunes</t>
+  </si>
+  <si>
+    <t>VILA NOVA</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Dr. Bruno Lima</t>
-  </si>
-  <si>
-    <t>Vet Amigo Fiel</t>
-  </si>
-  <si>
-    <t>Dra. Carla Nunes</t>
-  </si>
-  <si>
-    <t>Jardim das Flores</t>
-  </si>
-  <si>
-    <t>Hospital Veterinário São Francisco</t>
+    <t>HOSPITAL SÃO FRANCISCO</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 4500 - Vila Nova, Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>2x no mês em dias alternados</t>
   </si>
   <si>
     <t>Dr. Diego Alves</t>
   </si>
   <si>
-    <t>Vila Nova</t>
-  </si>
-  <si>
     <t>Dra. Elisa Prado</t>
   </si>
   <si>
-    <t>Clínica Bicho Manso</t>
+    <t>BOA VISTA</t>
+  </si>
+  <si>
+    <t>colocar dia 16 de outubro</t>
+  </si>
+  <si>
+    <t>VET AMIGO FIEL</t>
+  </si>
+  <si>
+    <t>Rua do Sol, 45 - Boa Vista, Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>1x no mês sempre sexta</t>
   </si>
   <si>
     <t>Dr. Fábio Rocha</t>
   </si>
   <si>
-    <t>Pet Center 24h</t>
+    <t>CLÍNICA BICHO MANSO</t>
+  </si>
+  <si>
+    <t>Rua Sete, 300 - Centro, Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>1x no mês terça ou quinta</t>
   </si>
   <si>
     <t>Dra. Gabriela Reis</t>
   </si>
   <si>
-    <t>Boa Vista</t>
-  </si>
-  <si>
-    <t>Sim</t>
+    <t>NOVO BAIRRO</t>
+  </si>
+  <si>
+    <t>PET CENTER 24H</t>
+  </si>
+  <si>
+    <t>Rua Nova, 10 - Novo Bairro, Rio de Janeiro - RJ</t>
+  </si>
+  <si>
+    <t>1x no mês de preferencia quarta</t>
   </si>
   <si>
     <t>Dr. Henrique Dias</t>
   </si>
   <si>
-    <t>Clínica Novo Bairro</t>
-  </si>
-  <si>
-    <t>Novo Bairro</t>
+    <t>DOMICILIO</t>
+  </si>
+  <si>
+    <t>veterinário que faço visita online, NÃO COLOCAR NO ROTEIRO</t>
   </si>
 </sst>
 </file>
@@ -475,7 +514,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -491,16 +530,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -513,47 +553,91 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
       <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -564,16 +648,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,47 +671,51 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -637,16 +726,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -659,47 +749,51 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
